--- a/PBStools/inst/sql/bio.fields.xlsx
+++ b/PBStools/inst/sql/bio.fields.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="480" yWindow="120" windowWidth="18195" windowHeight="7740" firstSheet="5" activeTab="20"/>
+    <workbookView xWindow="480" yWindow="120" windowWidth="18195" windowHeight="7740" firstSheet="5" activeTab="15"/>
   </bookViews>
   <sheets>
     <sheet name="bio.fields" sheetId="1" r:id="rId1"/>
@@ -20163,11 +20163,13 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="36">
